--- a/docs/design/ACSMS-SCR-027/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_ロール管理画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-027/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_ロール管理画面_V1.0.xlsx
@@ -1702,7 +1702,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2128,7 +2128,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2829,7 +2829,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3390,7 +3390,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4712,7 +4712,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -4726,21 +4726,21 @@
     <row r="54" ht="36" customHeight="1">
       <c r="C54" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：ログインユーザーの role_code が `NICHINO_ADMIN` であるか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
+          <t>権限チェック：`@Permissions('role.view')`（`seeder.md §2.14` permission_id=45）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
       <c r="D55" s="41" t="inlineStr">
         <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
+          <t>`m_roles_permissions` 上 `role.view` は NICHINO_ADMIN にのみ付与されているため、</t>
         </is>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="D56" s="41" t="inlineStr">
         <is>
-          <t>※ seeder.md にロール管理専用の permission_code は定義されていないため、ロール直接チェックとする。</t>
+          <t>実装は他コントローラと同じく `PermissionsGuard` + `@Permissions(...)` を使用し、</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK77"/>
+  <dimension ref="A1:AK81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -5114,7 +5114,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6279,14 +6279,14 @@
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="11" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="54" customHeight="1">
       <c r="B34" s="31" t="n">
         <v>7</v>
       </c>
       <c r="C34" s="38" t="n"/>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>locked_permission_ids</t>
         </is>
       </c>
       <c r="E34" s="10" t="n"/>
@@ -6299,7 +6299,7 @@
       <c r="L34" s="11" t="n"/>
       <c r="M34" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N34" s="10" t="n"/>
@@ -6307,16 +6307,12 @@
       <c r="P34" s="11" t="n"/>
       <c r="Q34" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R34" s="10" t="n"/>
       <c r="S34" s="11" t="n"/>
-      <c r="T34" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T34" s="17" t="inlineStr"/>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
       <c r="W34" s="10" t="n"/>
@@ -6334,7 +6330,7 @@
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>`permission_ids` のうち変更不可（システム必須・シード由来）な権限IDの配列。該当チェックボックスはFEでdisabled表示</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -6347,10 +6343,10 @@
       <c r="B35" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="C35" s="39" t="n"/>
+      <c r="C35" s="38" t="n"/>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E35" s="10" t="n"/>
@@ -6387,7 +6383,7 @@
       <c r="X35" s="11" t="n"/>
       <c r="Y35" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z35" s="10" t="n"/>
@@ -6398,7 +6394,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -6407,64 +6403,128 @@
       <c r="AJ35" s="10" t="n"/>
       <c r="AK35" s="11" t="n"/>
     </row>
-    <row r="36" ht="19.5" customHeight="1"/>
-    <row r="37" ht="19.5" customHeight="1">
-      <c r="B37" s="40" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" s="39" t="n"/>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="10" t="n"/>
+      <c r="K36" s="10" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="11" t="n"/>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="11" t="n"/>
+      <c r="T36" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U36" s="10" t="n"/>
+      <c r="V36" s="10" t="n"/>
+      <c r="W36" s="10" t="n"/>
+      <c r="X36" s="11" t="n"/>
+      <c r="Y36" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z36" s="10" t="n"/>
+      <c r="AA36" s="10" t="n"/>
+      <c r="AB36" s="10" t="n"/>
+      <c r="AC36" s="10" t="n"/>
+      <c r="AD36" s="10" t="n"/>
+      <c r="AE36" s="11" t="n"/>
+      <c r="AF36" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG36" s="10" t="n"/>
+      <c r="AH36" s="10" t="n"/>
+      <c r="AI36" s="10" t="n"/>
+      <c r="AJ36" s="10" t="n"/>
+      <c r="AK36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1"/>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="C38" s="19" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/roles/1</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
-      <c r="H38" s="10" t="n"/>
-      <c r="I38" s="10" t="n"/>
-      <c r="J38" s="10" t="n"/>
-      <c r="K38" s="10" t="n"/>
-      <c r="L38" s="10" t="n"/>
-      <c r="M38" s="10" t="n"/>
-      <c r="N38" s="10" t="n"/>
-      <c r="O38" s="10" t="n"/>
-      <c r="P38" s="10" t="n"/>
-      <c r="Q38" s="10" t="n"/>
-      <c r="R38" s="10" t="n"/>
-      <c r="S38" s="10" t="n"/>
-      <c r="T38" s="10" t="n"/>
-      <c r="U38" s="10" t="n"/>
-      <c r="V38" s="10" t="n"/>
-      <c r="W38" s="10" t="n"/>
-      <c r="X38" s="10" t="n"/>
-      <c r="Y38" s="10" t="n"/>
-      <c r="Z38" s="10" t="n"/>
-      <c r="AA38" s="10" t="n"/>
-      <c r="AB38" s="10" t="n"/>
-      <c r="AC38" s="10" t="n"/>
-      <c r="AD38" s="10" t="n"/>
-      <c r="AE38" s="10" t="n"/>
-      <c r="AF38" s="10" t="n"/>
-      <c r="AG38" s="10" t="n"/>
-      <c r="AH38" s="10" t="n"/>
-      <c r="AI38" s="10" t="n"/>
-      <c r="AJ38" s="10" t="n"/>
-      <c r="AK38" s="11" t="n"/>
-    </row>
-    <row r="40" ht="19.5" customHeight="1">
-      <c r="B40" s="40" t="inlineStr">
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="10" t="n"/>
+      <c r="L39" s="10" t="n"/>
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="10" t="n"/>
+      <c r="P39" s="10" t="n"/>
+      <c r="Q39" s="10" t="n"/>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="10" t="n"/>
+      <c r="T39" s="10" t="n"/>
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="10" t="n"/>
+      <c r="W39" s="10" t="n"/>
+      <c r="X39" s="10" t="n"/>
+      <c r="Y39" s="10" t="n"/>
+      <c r="Z39" s="10" t="n"/>
+      <c r="AA39" s="10" t="n"/>
+      <c r="AB39" s="10" t="n"/>
+      <c r="AC39" s="10" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="10" t="n"/>
+      <c r="AF39" s="10" t="n"/>
+      <c r="AG39" s="10" t="n"/>
+      <c r="AH39" s="10" t="n"/>
+      <c r="AI39" s="10" t="n"/>
+      <c r="AJ39" s="10" t="n"/>
+      <c r="AK39" s="11" t="n"/>
+    </row>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="198" customHeight="1">
-      <c r="C41" s="19" t="inlineStr">
+    <row r="42" ht="216" customHeight="1">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -6473,56 +6533,57 @@
     "role_name": "日農（管理者）",
     "description": "日本農業新聞 管理者アカウント",
     "permission_ids": [16, 17, 18, 19, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38],
+    "locked_permission_ids": [16, 17, 18, 19, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38],
     "created_at": "2026-01-01T00:00:00Z",
     "updated_at": "2026-01-01T00:00:00Z"
   }
 }</t>
         </is>
       </c>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-      <c r="G41" s="10" t="n"/>
-      <c r="H41" s="10" t="n"/>
-      <c r="I41" s="10" t="n"/>
-      <c r="J41" s="10" t="n"/>
-      <c r="K41" s="10" t="n"/>
-      <c r="L41" s="10" t="n"/>
-      <c r="M41" s="10" t="n"/>
-      <c r="N41" s="10" t="n"/>
-      <c r="O41" s="10" t="n"/>
-      <c r="P41" s="10" t="n"/>
-      <c r="Q41" s="10" t="n"/>
-      <c r="R41" s="10" t="n"/>
-      <c r="S41" s="10" t="n"/>
-      <c r="T41" s="10" t="n"/>
-      <c r="U41" s="10" t="n"/>
-      <c r="V41" s="10" t="n"/>
-      <c r="W41" s="10" t="n"/>
-      <c r="X41" s="10" t="n"/>
-      <c r="Y41" s="10" t="n"/>
-      <c r="Z41" s="10" t="n"/>
-      <c r="AA41" s="10" t="n"/>
-      <c r="AB41" s="10" t="n"/>
-      <c r="AC41" s="10" t="n"/>
-      <c r="AD41" s="10" t="n"/>
-      <c r="AE41" s="10" t="n"/>
-      <c r="AF41" s="10" t="n"/>
-      <c r="AG41" s="10" t="n"/>
-      <c r="AH41" s="10" t="n"/>
-      <c r="AI41" s="10" t="n"/>
-      <c r="AJ41" s="10" t="n"/>
-      <c r="AK41" s="11" t="n"/>
-    </row>
-    <row r="43" ht="19.5" customHeight="1">
-      <c r="B43" s="40" t="inlineStr">
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="10" t="n"/>
+      <c r="Q42" s="10" t="n"/>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="10" t="n"/>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="10" t="n"/>
+      <c r="W42" s="10" t="n"/>
+      <c r="X42" s="10" t="n"/>
+      <c r="Y42" s="10" t="n"/>
+      <c r="Z42" s="10" t="n"/>
+      <c r="AA42" s="10" t="n"/>
+      <c r="AB42" s="10" t="n"/>
+      <c r="AC42" s="10" t="n"/>
+      <c r="AD42" s="10" t="n"/>
+      <c r="AE42" s="10" t="n"/>
+      <c r="AF42" s="10" t="n"/>
+      <c r="AG42" s="10" t="n"/>
+      <c r="AH42" s="10" t="n"/>
+      <c r="AI42" s="10" t="n"/>
+      <c r="AJ42" s="10" t="n"/>
+      <c r="AK42" s="11" t="n"/>
+    </row>
+    <row r="44" ht="19.5" customHeight="1">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="72" customHeight="1">
-      <c r="C44" s="19" t="inlineStr">
+    <row r="45" ht="72" customHeight="1">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -6530,50 +6591,50 @@
 }</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="n"/>
-      <c r="J44" s="10" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="10" t="n"/>
-      <c r="M44" s="10" t="n"/>
-      <c r="N44" s="10" t="n"/>
-      <c r="O44" s="10" t="n"/>
-      <c r="P44" s="10" t="n"/>
-      <c r="Q44" s="10" t="n"/>
-      <c r="R44" s="10" t="n"/>
-      <c r="S44" s="10" t="n"/>
-      <c r="T44" s="10" t="n"/>
-      <c r="U44" s="10" t="n"/>
-      <c r="V44" s="10" t="n"/>
-      <c r="W44" s="10" t="n"/>
-      <c r="X44" s="10" t="n"/>
-      <c r="Y44" s="10" t="n"/>
-      <c r="Z44" s="10" t="n"/>
-      <c r="AA44" s="10" t="n"/>
-      <c r="AB44" s="10" t="n"/>
-      <c r="AC44" s="10" t="n"/>
-      <c r="AD44" s="10" t="n"/>
-      <c r="AE44" s="10" t="n"/>
-      <c r="AF44" s="10" t="n"/>
-      <c r="AG44" s="10" t="n"/>
-      <c r="AH44" s="10" t="n"/>
-      <c r="AI44" s="10" t="n"/>
-      <c r="AJ44" s="10" t="n"/>
-      <c r="AK44" s="11" t="n"/>
-    </row>
-    <row r="46" ht="19.5" customHeight="1">
-      <c r="B46" s="40" t="inlineStr">
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="10" t="n"/>
+      <c r="K45" s="10" t="n"/>
+      <c r="L45" s="10" t="n"/>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="10" t="n"/>
+      <c r="O45" s="10" t="n"/>
+      <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="10" t="n"/>
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="10" t="n"/>
+      <c r="U45" s="10" t="n"/>
+      <c r="V45" s="10" t="n"/>
+      <c r="W45" s="10" t="n"/>
+      <c r="X45" s="10" t="n"/>
+      <c r="Y45" s="10" t="n"/>
+      <c r="Z45" s="10" t="n"/>
+      <c r="AA45" s="10" t="n"/>
+      <c r="AB45" s="10" t="n"/>
+      <c r="AC45" s="10" t="n"/>
+      <c r="AD45" s="10" t="n"/>
+      <c r="AE45" s="10" t="n"/>
+      <c r="AF45" s="10" t="n"/>
+      <c r="AG45" s="10" t="n"/>
+      <c r="AH45" s="10" t="n"/>
+      <c r="AI45" s="10" t="n"/>
+      <c r="AJ45" s="10" t="n"/>
+      <c r="AK45" s="11" t="n"/>
+    </row>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="72" customHeight="1">
-      <c r="C47" s="19" t="inlineStr">
+    <row r="48" ht="72" customHeight="1">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -6581,50 +6642,50 @@
 }</t>
         </is>
       </c>
-      <c r="D47" s="10" t="n"/>
-      <c r="E47" s="10" t="n"/>
-      <c r="F47" s="10" t="n"/>
-      <c r="G47" s="10" t="n"/>
-      <c r="H47" s="10" t="n"/>
-      <c r="I47" s="10" t="n"/>
-      <c r="J47" s="10" t="n"/>
-      <c r="K47" s="10" t="n"/>
-      <c r="L47" s="10" t="n"/>
-      <c r="M47" s="10" t="n"/>
-      <c r="N47" s="10" t="n"/>
-      <c r="O47" s="10" t="n"/>
-      <c r="P47" s="10" t="n"/>
-      <c r="Q47" s="10" t="n"/>
-      <c r="R47" s="10" t="n"/>
-      <c r="S47" s="10" t="n"/>
-      <c r="T47" s="10" t="n"/>
-      <c r="U47" s="10" t="n"/>
-      <c r="V47" s="10" t="n"/>
-      <c r="W47" s="10" t="n"/>
-      <c r="X47" s="10" t="n"/>
-      <c r="Y47" s="10" t="n"/>
-      <c r="Z47" s="10" t="n"/>
-      <c r="AA47" s="10" t="n"/>
-      <c r="AB47" s="10" t="n"/>
-      <c r="AC47" s="10" t="n"/>
-      <c r="AD47" s="10" t="n"/>
-      <c r="AE47" s="10" t="n"/>
-      <c r="AF47" s="10" t="n"/>
-      <c r="AG47" s="10" t="n"/>
-      <c r="AH47" s="10" t="n"/>
-      <c r="AI47" s="10" t="n"/>
-      <c r="AJ47" s="10" t="n"/>
-      <c r="AK47" s="11" t="n"/>
-    </row>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="B49" s="40" t="inlineStr">
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="10" t="n"/>
+      <c r="K48" s="10" t="n"/>
+      <c r="L48" s="10" t="n"/>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="10" t="n"/>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="10" t="n"/>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="10" t="n"/>
+      <c r="T48" s="10" t="n"/>
+      <c r="U48" s="10" t="n"/>
+      <c r="V48" s="10" t="n"/>
+      <c r="W48" s="10" t="n"/>
+      <c r="X48" s="10" t="n"/>
+      <c r="Y48" s="10" t="n"/>
+      <c r="Z48" s="10" t="n"/>
+      <c r="AA48" s="10" t="n"/>
+      <c r="AB48" s="10" t="n"/>
+      <c r="AC48" s="10" t="n"/>
+      <c r="AD48" s="10" t="n"/>
+      <c r="AE48" s="10" t="n"/>
+      <c r="AF48" s="10" t="n"/>
+      <c r="AG48" s="10" t="n"/>
+      <c r="AH48" s="10" t="n"/>
+      <c r="AI48" s="10" t="n"/>
+      <c r="AJ48" s="10" t="n"/>
+      <c r="AK48" s="11" t="n"/>
+    </row>
+    <row r="50" ht="19.5" customHeight="1">
+      <c r="B50" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="72" customHeight="1">
-      <c r="C50" s="19" t="inlineStr">
+    <row r="51" ht="72" customHeight="1">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -6632,50 +6693,50 @@
 }</t>
         </is>
       </c>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="10" t="n"/>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="10" t="n"/>
-      <c r="H50" s="10" t="n"/>
-      <c r="I50" s="10" t="n"/>
-      <c r="J50" s="10" t="n"/>
-      <c r="K50" s="10" t="n"/>
-      <c r="L50" s="10" t="n"/>
-      <c r="M50" s="10" t="n"/>
-      <c r="N50" s="10" t="n"/>
-      <c r="O50" s="10" t="n"/>
-      <c r="P50" s="10" t="n"/>
-      <c r="Q50" s="10" t="n"/>
-      <c r="R50" s="10" t="n"/>
-      <c r="S50" s="10" t="n"/>
-      <c r="T50" s="10" t="n"/>
-      <c r="U50" s="10" t="n"/>
-      <c r="V50" s="10" t="n"/>
-      <c r="W50" s="10" t="n"/>
-      <c r="X50" s="10" t="n"/>
-      <c r="Y50" s="10" t="n"/>
-      <c r="Z50" s="10" t="n"/>
-      <c r="AA50" s="10" t="n"/>
-      <c r="AB50" s="10" t="n"/>
-      <c r="AC50" s="10" t="n"/>
-      <c r="AD50" s="10" t="n"/>
-      <c r="AE50" s="10" t="n"/>
-      <c r="AF50" s="10" t="n"/>
-      <c r="AG50" s="10" t="n"/>
-      <c r="AH50" s="10" t="n"/>
-      <c r="AI50" s="10" t="n"/>
-      <c r="AJ50" s="10" t="n"/>
-      <c r="AK50" s="11" t="n"/>
-    </row>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="B52" s="40" t="inlineStr">
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="10" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="10" t="n"/>
+      <c r="Q51" s="10" t="n"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="10" t="n"/>
+      <c r="Y51" s="10" t="n"/>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="10" t="n"/>
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="10" t="n"/>
+      <c r="AF51" s="10" t="n"/>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="10" t="n"/>
+      <c r="AJ51" s="10" t="n"/>
+      <c r="AK51" s="11" t="n"/>
+    </row>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="B53" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="72" customHeight="1">
-      <c r="C53" s="19" t="inlineStr">
+    <row r="54" ht="72" customHeight="1">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -6683,142 +6744,149 @@
 }</t>
         </is>
       </c>
-      <c r="D53" s="10" t="n"/>
-      <c r="E53" s="10" t="n"/>
-      <c r="F53" s="10" t="n"/>
-      <c r="G53" s="10" t="n"/>
-      <c r="H53" s="10" t="n"/>
-      <c r="I53" s="10" t="n"/>
-      <c r="J53" s="10" t="n"/>
-      <c r="K53" s="10" t="n"/>
-      <c r="L53" s="10" t="n"/>
-      <c r="M53" s="10" t="n"/>
-      <c r="N53" s="10" t="n"/>
-      <c r="O53" s="10" t="n"/>
-      <c r="P53" s="10" t="n"/>
-      <c r="Q53" s="10" t="n"/>
-      <c r="R53" s="10" t="n"/>
-      <c r="S53" s="10" t="n"/>
-      <c r="T53" s="10" t="n"/>
-      <c r="U53" s="10" t="n"/>
-      <c r="V53" s="10" t="n"/>
-      <c r="W53" s="10" t="n"/>
-      <c r="X53" s="10" t="n"/>
-      <c r="Y53" s="10" t="n"/>
-      <c r="Z53" s="10" t="n"/>
-      <c r="AA53" s="10" t="n"/>
-      <c r="AB53" s="10" t="n"/>
-      <c r="AC53" s="10" t="n"/>
-      <c r="AD53" s="10" t="n"/>
-      <c r="AE53" s="10" t="n"/>
-      <c r="AF53" s="10" t="n"/>
-      <c r="AG53" s="10" t="n"/>
-      <c r="AH53" s="10" t="n"/>
-      <c r="AI53" s="10" t="n"/>
-      <c r="AJ53" s="10" t="n"/>
-      <c r="AK53" s="11" t="n"/>
-    </row>
-    <row r="55" ht="19.5" customHeight="1"/>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AF54" s="10" t="n"/>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1"/>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="B57" s="27" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="C58" s="41" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="C59" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="D59" s="41" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="D60" s="41" t="inlineStr">
         <is>
           <t>role_id：数値型チェック、必須チェック</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="C60" s="41" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="C61" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="D61" s="41" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="D62" s="41" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="B62" s="27" t="inlineStr">
+    <row r="63" ht="18" customHeight="1">
+      <c r="B63" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="C63" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="C64" s="41" t="inlineStr">
         <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="C65" s="41" t="inlineStr">
+        <is>
           <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="36" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：ログインユーザーの role_code が `NICHINO_ADMIN` であるか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="D66" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="C67" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="B68" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得</t>
+    <row r="66" ht="36" customHeight="1">
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`@Permissions('role.view')`（`seeder.md §2.14` permission_id=45）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1">
+      <c r="D67" s="41" t="inlineStr">
+        <is>
+          <t>`m_roles_permissions` 上 `role.view` は NICHINO_ADMIN にのみ付与されているため、</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="D68" s="41" t="inlineStr">
+        <is>
+          <t>実装は他コントローラと同じく `PermissionsGuard` + `@Permissions(...)` を使用し、</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="C69" s="41" t="inlineStr">
         <is>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="B70" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="C71" s="41" t="inlineStr">
+        <is>
           <t>ロール基本情報を取得する。</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="72" customHeight="1">
-      <c r="C70" s="42" t="inlineStr">
+    <row r="72" ht="72" customHeight="1">
+      <c r="C72" s="42" t="inlineStr">
         <is>
           <t>SELECT role_id, role_code, role_name, description, created_at, updated_at
 FROM m_roles
@@ -6826,57 +6894,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="10" t="n"/>
-      <c r="Q70" s="10" t="n"/>
-      <c r="R70" s="10" t="n"/>
-      <c r="S70" s="10" t="n"/>
-      <c r="T70" s="10" t="n"/>
-      <c r="U70" s="10" t="n"/>
-      <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n"/>
-      <c r="X70" s="10" t="n"/>
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-      <c r="AA70" s="10" t="n"/>
-      <c r="AB70" s="10" t="n"/>
-      <c r="AC70" s="10" t="n"/>
-      <c r="AD70" s="10" t="n"/>
-      <c r="AE70" s="10" t="n"/>
-      <c r="AF70" s="10" t="n"/>
-      <c r="AG70" s="10" t="n"/>
-      <c r="AH70" s="10" t="n"/>
-      <c r="AI70" s="10" t="n"/>
-      <c r="AJ70" s="10" t="n"/>
-      <c r="AK70" s="11" t="n"/>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
+      <c r="AK72" s="11" t="n"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="C73" s="41" t="inlineStr">
         <is>
           <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="C72" s="41" t="inlineStr">
-        <is>
-          <t>ロールに紐付く権限ID一覧を取得する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="90" customHeight="1">
-      <c r="C73" s="42" t="inlineStr">
+    <row r="74" ht="18" customHeight="1">
+      <c r="C74" s="41" t="inlineStr">
+        <is>
+          <t>ロールに紐付く権限ID一覧を取得する（有効な全件、`permission_ids` 用）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="90" customHeight="1">
+      <c r="C75" s="42" t="inlineStr">
         <is>
           <t>SELECT permission_id
 FROM m_roles_permissions
@@ -6885,79 +6953,133 @@
 ORDER BY permission_id ASC</t>
         </is>
       </c>
-      <c r="D73" s="10" t="n"/>
-      <c r="E73" s="10" t="n"/>
-      <c r="F73" s="10" t="n"/>
-      <c r="G73" s="10" t="n"/>
-      <c r="H73" s="10" t="n"/>
-      <c r="I73" s="10" t="n"/>
-      <c r="J73" s="10" t="n"/>
-      <c r="K73" s="10" t="n"/>
-      <c r="L73" s="10" t="n"/>
-      <c r="M73" s="10" t="n"/>
-      <c r="N73" s="10" t="n"/>
-      <c r="O73" s="10" t="n"/>
-      <c r="P73" s="10" t="n"/>
-      <c r="Q73" s="10" t="n"/>
-      <c r="R73" s="10" t="n"/>
-      <c r="S73" s="10" t="n"/>
-      <c r="T73" s="10" t="n"/>
-      <c r="U73" s="10" t="n"/>
-      <c r="V73" s="10" t="n"/>
-      <c r="W73" s="10" t="n"/>
-      <c r="X73" s="10" t="n"/>
-      <c r="Y73" s="10" t="n"/>
-      <c r="Z73" s="10" t="n"/>
-      <c r="AA73" s="10" t="n"/>
-      <c r="AB73" s="10" t="n"/>
-      <c r="AC73" s="10" t="n"/>
-      <c r="AD73" s="10" t="n"/>
-      <c r="AE73" s="10" t="n"/>
-      <c r="AF73" s="10" t="n"/>
-      <c r="AG73" s="10" t="n"/>
-      <c r="AH73" s="10" t="n"/>
-      <c r="AI73" s="10" t="n"/>
-      <c r="AJ73" s="10" t="n"/>
-      <c r="AK73" s="11" t="n"/>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="B74" s="27" t="inlineStr">
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="10" t="n"/>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="10" t="n"/>
+      <c r="X75" s="10" t="n"/>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="10" t="n"/>
+      <c r="AE75" s="10" t="n"/>
+      <c r="AF75" s="10" t="n"/>
+      <c r="AG75" s="10" t="n"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="10" t="n"/>
+      <c r="AJ75" s="10" t="n"/>
+      <c r="AK75" s="11" t="n"/>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="C76" s="41" t="inlineStr">
+        <is>
+          <t>ロールに紐付く権限のうち、変更不可（`locked = TRUE`）な行のみ取得する（`locked_permission_ids` 用）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="108" customHeight="1">
+      <c r="C77" s="42" t="inlineStr">
+        <is>
+          <t>SELECT permission_id
+FROM m_roles_permissions
+WHERE role_id = :role_id
+  AND deleted_at IS NULL
+  AND locked = TRUE
+ORDER BY permission_id ASC</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="10" t="n"/>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="10" t="n"/>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="10" t="n"/>
+      <c r="Y77" s="10" t="n"/>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="10" t="n"/>
+      <c r="AE77" s="10" t="n"/>
+      <c r="AF77" s="10" t="n"/>
+      <c r="AG77" s="10" t="n"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="10" t="n"/>
+      <c r="AJ77" s="10" t="n"/>
+      <c r="AK77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="27" t="inlineStr">
         <is>
           <t>4.4 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="C75" s="41" t="inlineStr">
-        <is>
-          <t>ロール基本情報と権限ID配列を data オブジェクトとして返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="B76" s="27" t="inlineStr">
+    <row r="79" ht="36" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
+        <is>
+          <t>ロール基本情報・権限ID配列・変更不可権限ID配列を data オブジェクトとして返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="C77" s="41" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="145">
+  <mergeCells count="154">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y27:AE27"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="Y36:AE36"/>
+    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C53:AK53"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="C77:AK77"/>
@@ -6966,46 +7088,53 @@
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
+    <mergeCell ref="C29:C36"/>
+    <mergeCell ref="C45:AK45"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="C65:AK65"/>
     <mergeCell ref="D33:L33"/>
-    <mergeCell ref="C44:AK44"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="D35:L35"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
+    <mergeCell ref="B63:AK63"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="C51:AK51"/>
     <mergeCell ref="D34:L34"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="T34:X34"/>
-    <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="D61:AK61"/>
-    <mergeCell ref="C38:AK38"/>
+    <mergeCell ref="C48:AK48"/>
+    <mergeCell ref="D36:L36"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="T30:X30"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="A57:AK57"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="C42:AK42"/>
+    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="AD2:AG3"/>
@@ -7016,18 +7145,23 @@
     <mergeCell ref="Y30:AE30"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="B49:I49"/>
     <mergeCell ref="Y29:AE29"/>
+    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="A25:AK25"/>
-    <mergeCell ref="C29:C35"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="Y31:AE31"/>
-    <mergeCell ref="D66:AK66"/>
+    <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="C39:AK39"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B50:I50"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="M36:P36"/>
+    <mergeCell ref="C81:AK81"/>
+    <mergeCell ref="B58:AK58"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="T32:X32"/>
@@ -7035,63 +7169,59 @@
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="B57:AK57"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="Q36:S36"/>
     <mergeCell ref="C64:AK64"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
+    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="C54:AK54"/>
     <mergeCell ref="D30:L30"/>
-    <mergeCell ref="C63:AK63"/>
-    <mergeCell ref="C41:AK41"/>
-    <mergeCell ref="C50:AK50"/>
     <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="B38:I38"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
+    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
-    <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="A56:AK56"/>
+    <mergeCell ref="T36:X36"/>
     <mergeCell ref="C27:L27"/>
-    <mergeCell ref="C67:AK67"/>
     <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B70:AK70"/>
     <mergeCell ref="D32:L32"/>
     <mergeCell ref="C69:AK69"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B52:I52"/>
     <mergeCell ref="Y32:AE32"/>
+    <mergeCell ref="D68:AK68"/>
+    <mergeCell ref="D67:AK67"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D59:AK59"/>
-    <mergeCell ref="C47:AK47"/>
-    <mergeCell ref="B74:AK74"/>
-    <mergeCell ref="B68:AK68"/>
+    <mergeCell ref="D60:AK60"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B53:I53"/>
     <mergeCell ref="AF28:AK28"/>
-    <mergeCell ref="B37:I37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="B76:AK76"/>
-    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="M22:P22"/>
+    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="D31:L31"/>
-    <mergeCell ref="B62:AK62"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="AF29:AK29"/>
@@ -7106,7 +7236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK99"/>
+  <dimension ref="A1:AK102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -7267,7 +7397,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7673,7 +7803,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>正常にロールを更新しました</t>
+          <t>更新しました</t>
         </is>
       </c>
       <c r="O14" s="10" t="n"/>
@@ -8656,14 +8786,14 @@
       <c r="AJ37" s="10" t="n"/>
       <c r="AK37" s="11" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1">
+    <row r="38" ht="36" customHeight="1">
       <c r="B38" s="31" t="n">
         <v>7</v>
       </c>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>locked_permission_ids</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -8676,7 +8806,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -8684,16 +8814,12 @@
       <c r="P38" s="11" t="n"/>
       <c r="Q38" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R38" s="10" t="n"/>
       <c r="S38" s="11" t="n"/>
-      <c r="T38" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T38" s="17" t="inlineStr"/>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
       <c r="W38" s="10" t="n"/>
@@ -8711,7 +8837,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>`permission_ids` のうち変更不可（システム必須・シード由来）な権限IDの配列</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -8724,10 +8850,10 @@
       <c r="B39" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="C39" s="39" t="n"/>
+      <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -8764,7 +8890,7 @@
       <c r="X39" s="11" t="n"/>
       <c r="Y39" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z39" s="10" t="n"/>
@@ -8775,7 +8901,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -8784,16 +8910,80 @@
       <c r="AJ39" s="10" t="n"/>
       <c r="AK39" s="11" t="n"/>
     </row>
-    <row r="40" ht="19.5" customHeight="1"/>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="B41" s="40" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" s="39" t="n"/>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="11" t="n"/>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="11" t="n"/>
+      <c r="T40" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="10" t="n"/>
+      <c r="X40" s="11" t="n"/>
+      <c r="Y40" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="10" t="n"/>
+      <c r="AB40" s="10" t="n"/>
+      <c r="AC40" s="10" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG40" s="10" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="10" t="n"/>
+      <c r="AJ40" s="10" t="n"/>
+      <c r="AK40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="19.5" customHeight="1"/>
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="144" customHeight="1">
-      <c r="C42" s="19" t="inlineStr">
+    <row r="43" ht="144" customHeight="1">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>PUT /api/v1/roles/3
 Content-Type: application/json
@@ -8804,50 +8994,50 @@
 }</t>
         </is>
       </c>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="10" t="n"/>
-      <c r="J42" s="10" t="n"/>
-      <c r="K42" s="10" t="n"/>
-      <c r="L42" s="10" t="n"/>
-      <c r="M42" s="10" t="n"/>
-      <c r="N42" s="10" t="n"/>
-      <c r="O42" s="10" t="n"/>
-      <c r="P42" s="10" t="n"/>
-      <c r="Q42" s="10" t="n"/>
-      <c r="R42" s="10" t="n"/>
-      <c r="S42" s="10" t="n"/>
-      <c r="T42" s="10" t="n"/>
-      <c r="U42" s="10" t="n"/>
-      <c r="V42" s="10" t="n"/>
-      <c r="W42" s="10" t="n"/>
-      <c r="X42" s="10" t="n"/>
-      <c r="Y42" s="10" t="n"/>
-      <c r="Z42" s="10" t="n"/>
-      <c r="AA42" s="10" t="n"/>
-      <c r="AB42" s="10" t="n"/>
-      <c r="AC42" s="10" t="n"/>
-      <c r="AD42" s="10" t="n"/>
-      <c r="AE42" s="10" t="n"/>
-      <c r="AF42" s="10" t="n"/>
-      <c r="AG42" s="10" t="n"/>
-      <c r="AH42" s="10" t="n"/>
-      <c r="AI42" s="10" t="n"/>
-      <c r="AJ42" s="10" t="n"/>
-      <c r="AK42" s="11" t="n"/>
-    </row>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="B44" s="40" t="inlineStr">
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="10" t="n"/>
+      <c r="L43" s="10" t="n"/>
+      <c r="M43" s="10" t="n"/>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="10" t="n"/>
+      <c r="P43" s="10" t="n"/>
+      <c r="Q43" s="10" t="n"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="10" t="n"/>
+      <c r="T43" s="10" t="n"/>
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="10" t="n"/>
+      <c r="W43" s="10" t="n"/>
+      <c r="X43" s="10" t="n"/>
+      <c r="Y43" s="10" t="n"/>
+      <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="10" t="n"/>
+      <c r="AB43" s="10" t="n"/>
+      <c r="AC43" s="10" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="10" t="n"/>
+      <c r="AF43" s="10" t="n"/>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="10" t="n"/>
+      <c r="AI43" s="10" t="n"/>
+      <c r="AJ43" s="10" t="n"/>
+      <c r="AK43" s="11" t="n"/>
+    </row>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="198" customHeight="1">
-      <c r="C45" s="19" t="inlineStr">
+    <row r="46" ht="216" customHeight="1">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -8856,56 +9046,57 @@
     "role_name": "中央会",
     "description": "中央会アカウント（更新）",
     "permission_ids": [1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 17, 18, 20, 21, 22, 23, 36, 37, 38, 39, 40, 41, 42, 43],
+    "locked_permission_ids": [1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15, 17, 18, 20, 21, 22, 23, 36, 37, 38, 39, 40, 41, 42, 43],
     "created_at": "2026-01-01T00:00:00Z",
     "updated_at": "2026-04-14T14:30:00Z"
   }
 }</t>
         </is>
       </c>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="10" t="n"/>
-      <c r="G45" s="10" t="n"/>
-      <c r="H45" s="10" t="n"/>
-      <c r="I45" s="10" t="n"/>
-      <c r="J45" s="10" t="n"/>
-      <c r="K45" s="10" t="n"/>
-      <c r="L45" s="10" t="n"/>
-      <c r="M45" s="10" t="n"/>
-      <c r="N45" s="10" t="n"/>
-      <c r="O45" s="10" t="n"/>
-      <c r="P45" s="10" t="n"/>
-      <c r="Q45" s="10" t="n"/>
-      <c r="R45" s="10" t="n"/>
-      <c r="S45" s="10" t="n"/>
-      <c r="T45" s="10" t="n"/>
-      <c r="U45" s="10" t="n"/>
-      <c r="V45" s="10" t="n"/>
-      <c r="W45" s="10" t="n"/>
-      <c r="X45" s="10" t="n"/>
-      <c r="Y45" s="10" t="n"/>
-      <c r="Z45" s="10" t="n"/>
-      <c r="AA45" s="10" t="n"/>
-      <c r="AB45" s="10" t="n"/>
-      <c r="AC45" s="10" t="n"/>
-      <c r="AD45" s="10" t="n"/>
-      <c r="AE45" s="10" t="n"/>
-      <c r="AF45" s="10" t="n"/>
-      <c r="AG45" s="10" t="n"/>
-      <c r="AH45" s="10" t="n"/>
-      <c r="AI45" s="10" t="n"/>
-      <c r="AJ45" s="10" t="n"/>
-      <c r="AK45" s="11" t="n"/>
-    </row>
-    <row r="47" ht="19.5" customHeight="1">
-      <c r="B47" s="40" t="inlineStr">
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="10" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="10" t="n"/>
+      <c r="Y46" s="10" t="n"/>
+      <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
+      <c r="AB46" s="10" t="n"/>
+      <c r="AC46" s="10" t="n"/>
+      <c r="AD46" s="10" t="n"/>
+      <c r="AE46" s="10" t="n"/>
+      <c r="AF46" s="10" t="n"/>
+      <c r="AG46" s="10" t="n"/>
+      <c r="AH46" s="10" t="n"/>
+      <c r="AI46" s="10" t="n"/>
+      <c r="AJ46" s="10" t="n"/>
+      <c r="AK46" s="11" t="n"/>
+    </row>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request）</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="126" customHeight="1">
-      <c r="C48" s="19" t="inlineStr">
+    <row r="49" ht="126" customHeight="1">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -8916,50 +9107,104 @@
 }</t>
         </is>
       </c>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
-      <c r="G48" s="10" t="n"/>
-      <c r="H48" s="10" t="n"/>
-      <c r="I48" s="10" t="n"/>
-      <c r="J48" s="10" t="n"/>
-      <c r="K48" s="10" t="n"/>
-      <c r="L48" s="10" t="n"/>
-      <c r="M48" s="10" t="n"/>
-      <c r="N48" s="10" t="n"/>
-      <c r="O48" s="10" t="n"/>
-      <c r="P48" s="10" t="n"/>
-      <c r="Q48" s="10" t="n"/>
-      <c r="R48" s="10" t="n"/>
-      <c r="S48" s="10" t="n"/>
-      <c r="T48" s="10" t="n"/>
-      <c r="U48" s="10" t="n"/>
-      <c r="V48" s="10" t="n"/>
-      <c r="W48" s="10" t="n"/>
-      <c r="X48" s="10" t="n"/>
-      <c r="Y48" s="10" t="n"/>
-      <c r="Z48" s="10" t="n"/>
-      <c r="AA48" s="10" t="n"/>
-      <c r="AB48" s="10" t="n"/>
-      <c r="AC48" s="10" t="n"/>
-      <c r="AD48" s="10" t="n"/>
-      <c r="AE48" s="10" t="n"/>
-      <c r="AF48" s="10" t="n"/>
-      <c r="AG48" s="10" t="n"/>
-      <c r="AH48" s="10" t="n"/>
-      <c r="AI48" s="10" t="n"/>
-      <c r="AJ48" s="10" t="n"/>
-      <c r="AK48" s="11" t="n"/>
-    </row>
-    <row r="50" ht="19.5" customHeight="1">
-      <c r="B50" s="40" t="inlineStr">
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="10" t="n"/>
+      <c r="K49" s="10" t="n"/>
+      <c r="L49" s="10" t="n"/>
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="10" t="n"/>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n"/>
+      <c r="U49" s="10" t="n"/>
+      <c r="V49" s="10" t="n"/>
+      <c r="W49" s="10" t="n"/>
+      <c r="X49" s="10" t="n"/>
+      <c r="Y49" s="10" t="n"/>
+      <c r="Z49" s="10" t="n"/>
+      <c r="AA49" s="10" t="n"/>
+      <c r="AB49" s="10" t="n"/>
+      <c r="AC49" s="10" t="n"/>
+      <c r="AD49" s="10" t="n"/>
+      <c r="AE49" s="10" t="n"/>
+      <c r="AF49" s="10" t="n"/>
+      <c r="AG49" s="10" t="n"/>
+      <c r="AH49" s="10" t="n"/>
+      <c r="AI49" s="10" t="n"/>
+      <c r="AJ49" s="10" t="n"/>
+      <c r="AK49" s="11" t="n"/>
+    </row>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="B51" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Bad Request（変更不可権限の解除））</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="126" customHeight="1">
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "VALIDATION_ERROR",
+  "message": "システム必須権限のため、解除できません。",
+  "errors": [
+    { "field": "permission_ids", "message": "次の権限はシステム必須のため解除できません: 2, 5" }
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="10" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="10" t="n"/>
+      <c r="Y52" s="10" t="n"/>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="10" t="n"/>
+      <c r="AF52" s="10" t="n"/>
+      <c r="AG52" s="10" t="n"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="10" t="n"/>
+      <c r="AJ52" s="10" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="72" customHeight="1">
-      <c r="C51" s="19" t="inlineStr">
+    <row r="55" ht="72" customHeight="1">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -8967,50 +9212,50 @@
 }</t>
         </is>
       </c>
-      <c r="D51" s="10" t="n"/>
-      <c r="E51" s="10" t="n"/>
-      <c r="F51" s="10" t="n"/>
-      <c r="G51" s="10" t="n"/>
-      <c r="H51" s="10" t="n"/>
-      <c r="I51" s="10" t="n"/>
-      <c r="J51" s="10" t="n"/>
-      <c r="K51" s="10" t="n"/>
-      <c r="L51" s="10" t="n"/>
-      <c r="M51" s="10" t="n"/>
-      <c r="N51" s="10" t="n"/>
-      <c r="O51" s="10" t="n"/>
-      <c r="P51" s="10" t="n"/>
-      <c r="Q51" s="10" t="n"/>
-      <c r="R51" s="10" t="n"/>
-      <c r="S51" s="10" t="n"/>
-      <c r="T51" s="10" t="n"/>
-      <c r="U51" s="10" t="n"/>
-      <c r="V51" s="10" t="n"/>
-      <c r="W51" s="10" t="n"/>
-      <c r="X51" s="10" t="n"/>
-      <c r="Y51" s="10" t="n"/>
-      <c r="Z51" s="10" t="n"/>
-      <c r="AA51" s="10" t="n"/>
-      <c r="AB51" s="10" t="n"/>
-      <c r="AC51" s="10" t="n"/>
-      <c r="AD51" s="10" t="n"/>
-      <c r="AE51" s="10" t="n"/>
-      <c r="AF51" s="10" t="n"/>
-      <c r="AG51" s="10" t="n"/>
-      <c r="AH51" s="10" t="n"/>
-      <c r="AI51" s="10" t="n"/>
-      <c r="AJ51" s="10" t="n"/>
-      <c r="AK51" s="11" t="n"/>
-    </row>
-    <row r="53" ht="19.5" customHeight="1">
-      <c r="B53" s="40" t="inlineStr">
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="10" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
+      <c r="Y55" s="10" t="n"/>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="10" t="n"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="10" t="n"/>
+      <c r="AF55" s="10" t="n"/>
+      <c r="AG55" s="10" t="n"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
+      <c r="AK55" s="11" t="n"/>
+    </row>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="B57" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="72" customHeight="1">
-      <c r="C54" s="19" t="inlineStr">
+    <row r="58" ht="72" customHeight="1">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -9018,50 +9263,50 @@
 }</t>
         </is>
       </c>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
-      <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
-      <c r="I54" s="10" t="n"/>
-      <c r="J54" s="10" t="n"/>
-      <c r="K54" s="10" t="n"/>
-      <c r="L54" s="10" t="n"/>
-      <c r="M54" s="10" t="n"/>
-      <c r="N54" s="10" t="n"/>
-      <c r="O54" s="10" t="n"/>
-      <c r="P54" s="10" t="n"/>
-      <c r="Q54" s="10" t="n"/>
-      <c r="R54" s="10" t="n"/>
-      <c r="S54" s="10" t="n"/>
-      <c r="T54" s="10" t="n"/>
-      <c r="U54" s="10" t="n"/>
-      <c r="V54" s="10" t="n"/>
-      <c r="W54" s="10" t="n"/>
-      <c r="X54" s="10" t="n"/>
-      <c r="Y54" s="10" t="n"/>
-      <c r="Z54" s="10" t="n"/>
-      <c r="AA54" s="10" t="n"/>
-      <c r="AB54" s="10" t="n"/>
-      <c r="AC54" s="10" t="n"/>
-      <c r="AD54" s="10" t="n"/>
-      <c r="AE54" s="10" t="n"/>
-      <c r="AF54" s="10" t="n"/>
-      <c r="AG54" s="10" t="n"/>
-      <c r="AH54" s="10" t="n"/>
-      <c r="AI54" s="10" t="n"/>
-      <c r="AJ54" s="10" t="n"/>
-      <c r="AK54" s="11" t="n"/>
-    </row>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="B56" s="40" t="inlineStr">
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AF58" s="10" t="n"/>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="72" customHeight="1">
-      <c r="C57" s="19" t="inlineStr">
+    <row r="61" ht="72" customHeight="1">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "NOT_FOUND",
@@ -9069,50 +9314,50 @@
 }</t>
         </is>
       </c>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="10" t="n"/>
-      <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
-      <c r="I57" s="10" t="n"/>
-      <c r="J57" s="10" t="n"/>
-      <c r="K57" s="10" t="n"/>
-      <c r="L57" s="10" t="n"/>
-      <c r="M57" s="10" t="n"/>
-      <c r="N57" s="10" t="n"/>
-      <c r="O57" s="10" t="n"/>
-      <c r="P57" s="10" t="n"/>
-      <c r="Q57" s="10" t="n"/>
-      <c r="R57" s="10" t="n"/>
-      <c r="S57" s="10" t="n"/>
-      <c r="T57" s="10" t="n"/>
-      <c r="U57" s="10" t="n"/>
-      <c r="V57" s="10" t="n"/>
-      <c r="W57" s="10" t="n"/>
-      <c r="X57" s="10" t="n"/>
-      <c r="Y57" s="10" t="n"/>
-      <c r="Z57" s="10" t="n"/>
-      <c r="AA57" s="10" t="n"/>
-      <c r="AB57" s="10" t="n"/>
-      <c r="AC57" s="10" t="n"/>
-      <c r="AD57" s="10" t="n"/>
-      <c r="AE57" s="10" t="n"/>
-      <c r="AF57" s="10" t="n"/>
-      <c r="AG57" s="10" t="n"/>
-      <c r="AH57" s="10" t="n"/>
-      <c r="AI57" s="10" t="n"/>
-      <c r="AJ57" s="10" t="n"/>
-      <c r="AK57" s="11" t="n"/>
-    </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="B59" s="40" t="inlineStr">
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="10" t="n"/>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="10" t="n"/>
+      <c r="X61" s="10" t="n"/>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="10" t="n"/>
+      <c r="AE61" s="10" t="n"/>
+      <c r="AF61" s="10" t="n"/>
+      <c r="AG61" s="10" t="n"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="10" t="n"/>
+      <c r="AJ61" s="10" t="n"/>
+      <c r="AK61" s="11" t="n"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="B63" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="72" customHeight="1">
-      <c r="C60" s="19" t="inlineStr">
+    <row r="64" ht="72" customHeight="1">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -9120,284 +9365,317 @@
 }</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="10" t="n"/>
-      <c r="F60" s="10" t="n"/>
-      <c r="G60" s="10" t="n"/>
-      <c r="H60" s="10" t="n"/>
-      <c r="I60" s="10" t="n"/>
-      <c r="J60" s="10" t="n"/>
-      <c r="K60" s="10" t="n"/>
-      <c r="L60" s="10" t="n"/>
-      <c r="M60" s="10" t="n"/>
-      <c r="N60" s="10" t="n"/>
-      <c r="O60" s="10" t="n"/>
-      <c r="P60" s="10" t="n"/>
-      <c r="Q60" s="10" t="n"/>
-      <c r="R60" s="10" t="n"/>
-      <c r="S60" s="10" t="n"/>
-      <c r="T60" s="10" t="n"/>
-      <c r="U60" s="10" t="n"/>
-      <c r="V60" s="10" t="n"/>
-      <c r="W60" s="10" t="n"/>
-      <c r="X60" s="10" t="n"/>
-      <c r="Y60" s="10" t="n"/>
-      <c r="Z60" s="10" t="n"/>
-      <c r="AA60" s="10" t="n"/>
-      <c r="AB60" s="10" t="n"/>
-      <c r="AC60" s="10" t="n"/>
-      <c r="AD60" s="10" t="n"/>
-      <c r="AE60" s="10" t="n"/>
-      <c r="AF60" s="10" t="n"/>
-      <c r="AG60" s="10" t="n"/>
-      <c r="AH60" s="10" t="n"/>
-      <c r="AI60" s="10" t="n"/>
-      <c r="AJ60" s="10" t="n"/>
-      <c r="AK60" s="11" t="n"/>
-    </row>
-    <row r="62" ht="19.5" customHeight="1"/>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="27" t="inlineStr">
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="10" t="n"/>
+      <c r="X64" s="10" t="n"/>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="10" t="n"/>
+      <c r="AE64" s="10" t="n"/>
+      <c r="AF64" s="10" t="n"/>
+      <c r="AG64" s="10" t="n"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="10" t="n"/>
+      <c r="AJ64" s="10" t="n"/>
+      <c r="AK64" s="11" t="n"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="1"/>
+    <row r="67" ht="19.5" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="B64" s="27" t="inlineStr">
+    <row r="68" ht="54" customHeight="1">
+      <c r="B68" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="10" t="n"/>
+      <c r="J68" s="10" t="n"/>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="10" t="n"/>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="10" t="n"/>
+      <c r="X68" s="10" t="n"/>
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="10" t="n"/>
+      <c r="AD68" s="10" t="n"/>
+      <c r="AE68" s="10" t="n"/>
+      <c r="AF68" s="10" t="n"/>
+      <c r="AG68" s="10" t="n"/>
+      <c r="AH68" s="10" t="n"/>
+      <c r="AI68" s="10" t="n"/>
+      <c r="AJ68" s="10" t="n"/>
+      <c r="AK68" s="11" t="n"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="B69" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
+    <row r="70" ht="18" customHeight="1">
+      <c r="C70" s="41" t="inlineStr">
         <is>
           <t>パスパラメータ：role_id 数値型チェック、必須</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="C66" s="41" t="inlineStr">
+    <row r="71" ht="18" customHeight="1">
+      <c r="C71" s="41" t="inlineStr">
         <is>
           <t>リクエストボディ：</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="D67" s="41" t="inlineStr">
+    <row r="72" ht="18" customHeight="1">
+      <c r="D72" s="41" t="inlineStr">
         <is>
           <t>role_name：必須、最大20桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="D68" s="41" t="inlineStr">
-        <is>
-          <t>description：空欄可、最大200桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="D69" s="41" t="inlineStr">
-        <is>
-          <t>permission_ids：必須、配列型（空配列可）。各要素は数値型。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="36" customHeight="1">
-      <c r="D70" s="41" t="inlineStr">
-        <is>
-          <t>permission_ids 内のすべての permission_id が m_permissions テーブルに存在するか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="180" customHeight="1">
-      <c r="C71" s="42" t="inlineStr">
-        <is>
-          <t>SELECT 1 FROM (
-  SELECT unnest(:permission_ids::bigint[]) AS permission_id
-) AS input
-WHERE NOT EXISTS (
-  SELECT 1
-  FROM m_permissions p
-  WHERE p.permission_id = input.permission_id
-    AND p.deleted_at IS NULL
-)
-LIMIT 1</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="n"/>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="10" t="n"/>
-      <c r="G71" s="10" t="n"/>
-      <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n"/>
-      <c r="J71" s="10" t="n"/>
-      <c r="K71" s="10" t="n"/>
-      <c r="L71" s="10" t="n"/>
-      <c r="M71" s="10" t="n"/>
-      <c r="N71" s="10" t="n"/>
-      <c r="O71" s="10" t="n"/>
-      <c r="P71" s="10" t="n"/>
-      <c r="Q71" s="10" t="n"/>
-      <c r="R71" s="10" t="n"/>
-      <c r="S71" s="10" t="n"/>
-      <c r="T71" s="10" t="n"/>
-      <c r="U71" s="10" t="n"/>
-      <c r="V71" s="10" t="n"/>
-      <c r="W71" s="10" t="n"/>
-      <c r="X71" s="10" t="n"/>
-      <c r="Y71" s="10" t="n"/>
-      <c r="Z71" s="10" t="n"/>
-      <c r="AA71" s="10" t="n"/>
-      <c r="AB71" s="10" t="n"/>
-      <c r="AC71" s="10" t="n"/>
-      <c r="AD71" s="10" t="n"/>
-      <c r="AE71" s="10" t="n"/>
-      <c r="AF71" s="10" t="n"/>
-      <c r="AG71" s="10" t="n"/>
-      <c r="AH71" s="10" t="n"/>
-      <c r="AI71" s="10" t="n"/>
-      <c r="AJ71" s="10" t="n"/>
-      <c r="AK71" s="11" t="n"/>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="C72" s="41" t="inlineStr">
-        <is>
-          <t>クエリが1行以上返される場合（存在しない permission_id がある）：</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="D73" s="41" t="inlineStr">
         <is>
-          <t>HTTP 400 (`VALIDATION_ERROR`)</t>
+          <t>description：空欄可、最大200桁</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="D74" s="41" t="inlineStr">
         <is>
-          <t>errors配列に「指定された権限が見つかりません」というメッセージを含める</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="B75" s="27" t="inlineStr">
+          <t>permission_ids：必須、配列型（空配列可）。各要素は数値型。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="36" customHeight="1">
+      <c r="D75" s="41" t="inlineStr">
+        <is>
+          <t>permission_ids 内のすべての permission_id が m_permissions テーブルに存在するか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="234" customHeight="1">
+      <c r="C76" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+- クエリが1行以上返される場合（存在しない permission_id がある）：
+  - HTTP 400 (`VALIDATION_ERROR`)
+  - errors配列に「指定された権限が見つかりません」というメッセージを含める
+- 現在有効な割当のうち `locked = TRUE`（システム必須・シード由来）の permission_id が
+  リクエストの permission_ids から外れている場合：
+  - HTTP 400 (`VALIDATION_ERROR`)
+  - message：「システム必須権限のため、解除できません。」
+  - errors配列に「次の権限はシステム必須のため解除できません: {対象permission_idのカンマ区切り}」
+    というメッセージを含める（field: `permission_ids`）
+  - このチェックはトランザクション開始前に行われ、対象ロールが存在しない場合は
+    このチェックより先に §4.3 の404が優先される。
+</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="10" t="n"/>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="10" t="n"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="10" t="n"/>
+      <c r="AE76" s="10" t="n"/>
+      <c r="AF76" s="10" t="n"/>
+      <c r="AG76" s="10" t="n"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="10" t="n"/>
+      <c r="AJ76" s="10" t="n"/>
+      <c r="AK76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="B77" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="C76" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="C77" s="41" t="inlineStr">
+    <row r="78" ht="18" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
         <is>
           <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="36" customHeight="1">
-      <c r="C78" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：ログインユーザーの role_code が `NICHINO_ADMIN` であるか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="D79" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
+    <row r="80" ht="36" customHeight="1">
       <c r="C80" s="41" t="inlineStr">
         <is>
+          <t>権限チェック：`@Permissions('role.view')`（`seeder.md §2.14` permission_id=45）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="D81" s="41" t="inlineStr">
+        <is>
+          <t>`m_roles_permissions` 上 `role.view` は NICHINO_ADMIN にのみ付与されているため、</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="D82" s="41" t="inlineStr">
+        <is>
+          <t>実装は他コントローラと同じく `PermissionsGuard` + `@Permissions(...)` を使用し、</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
+        <is>
           <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" s="27" t="inlineStr">
         <is>
           <t>4.3 対象レコードの存在確認</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="54" customHeight="1">
-      <c r="C82" s="42" t="inlineStr">
+    <row r="85" ht="54" customHeight="1">
+      <c r="C85" s="42" t="inlineStr">
         <is>
           <t>SELECT * FROM m_roles
 WHERE role_id = :role_id
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="10" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
-      <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="10" t="n"/>
-      <c r="M82" s="10" t="n"/>
-      <c r="N82" s="10" t="n"/>
-      <c r="O82" s="10" t="n"/>
-      <c r="P82" s="10" t="n"/>
-      <c r="Q82" s="10" t="n"/>
-      <c r="R82" s="10" t="n"/>
-      <c r="S82" s="10" t="n"/>
-      <c r="T82" s="10" t="n"/>
-      <c r="U82" s="10" t="n"/>
-      <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
-      <c r="X82" s="10" t="n"/>
-      <c r="Y82" s="10" t="n"/>
-      <c r="Z82" s="10" t="n"/>
-      <c r="AA82" s="10" t="n"/>
-      <c r="AB82" s="10" t="n"/>
-      <c r="AC82" s="10" t="n"/>
-      <c r="AD82" s="10" t="n"/>
-      <c r="AE82" s="10" t="n"/>
-      <c r="AF82" s="10" t="n"/>
-      <c r="AG82" s="10" t="n"/>
-      <c r="AH82" s="10" t="n"/>
-      <c r="AI82" s="10" t="n"/>
-      <c r="AJ82" s="10" t="n"/>
-      <c r="AK82" s="11" t="n"/>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="n"/>
+      <c r="J85" s="10" t="n"/>
+      <c r="K85" s="10" t="n"/>
+      <c r="L85" s="10" t="n"/>
+      <c r="M85" s="10" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
+      <c r="T85" s="10" t="n"/>
+      <c r="U85" s="10" t="n"/>
+      <c r="V85" s="10" t="n"/>
+      <c r="W85" s="10" t="n"/>
+      <c r="X85" s="10" t="n"/>
+      <c r="Y85" s="10" t="n"/>
+      <c r="Z85" s="10" t="n"/>
+      <c r="AA85" s="10" t="n"/>
+      <c r="AB85" s="10" t="n"/>
+      <c r="AC85" s="10" t="n"/>
+      <c r="AD85" s="10" t="n"/>
+      <c r="AE85" s="10" t="n"/>
+      <c r="AF85" s="10" t="n"/>
+      <c r="AG85" s="10" t="n"/>
+      <c r="AH85" s="10" t="n"/>
+      <c r="AI85" s="10" t="n"/>
+      <c r="AJ85" s="10" t="n"/>
+      <c r="AK85" s="11" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
         <is>
           <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="B84" s="27" t="inlineStr">
+    <row r="87" ht="18" customHeight="1">
+      <c r="B87" s="27" t="inlineStr">
         <is>
           <t>4.4 データ更新（トランザクション）</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="C85" s="41" t="inlineStr">
+    <row r="88" ht="18" customHeight="1">
+      <c r="C88" s="41" t="inlineStr">
         <is>
           <t>以下の処理をトランザクション内で実行する。</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="144" customHeight="1">
-      <c r="C86" s="42" t="inlineStr">
+    <row r="89" ht="144" customHeight="1">
+      <c r="C89" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_roles
 SET role_name = :role_name,
@@ -9409,43 +9687,43 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D86" s="10" t="n"/>
-      <c r="E86" s="10" t="n"/>
-      <c r="F86" s="10" t="n"/>
-      <c r="G86" s="10" t="n"/>
-      <c r="H86" s="10" t="n"/>
-      <c r="I86" s="10" t="n"/>
-      <c r="J86" s="10" t="n"/>
-      <c r="K86" s="10" t="n"/>
-      <c r="L86" s="10" t="n"/>
-      <c r="M86" s="10" t="n"/>
-      <c r="N86" s="10" t="n"/>
-      <c r="O86" s="10" t="n"/>
-      <c r="P86" s="10" t="n"/>
-      <c r="Q86" s="10" t="n"/>
-      <c r="R86" s="10" t="n"/>
-      <c r="S86" s="10" t="n"/>
-      <c r="T86" s="10" t="n"/>
-      <c r="U86" s="10" t="n"/>
-      <c r="V86" s="10" t="n"/>
-      <c r="W86" s="10" t="n"/>
-      <c r="X86" s="10" t="n"/>
-      <c r="Y86" s="10" t="n"/>
-      <c r="Z86" s="10" t="n"/>
-      <c r="AA86" s="10" t="n"/>
-      <c r="AB86" s="10" t="n"/>
-      <c r="AC86" s="10" t="n"/>
-      <c r="AD86" s="10" t="n"/>
-      <c r="AE86" s="10" t="n"/>
-      <c r="AF86" s="10" t="n"/>
-      <c r="AG86" s="10" t="n"/>
-      <c r="AH86" s="10" t="n"/>
-      <c r="AI86" s="10" t="n"/>
-      <c r="AJ86" s="10" t="n"/>
-      <c r="AK86" s="11" t="n"/>
-    </row>
-    <row r="87" ht="108" customHeight="1">
-      <c r="C87" s="42" t="inlineStr">
+      <c r="D89" s="10" t="n"/>
+      <c r="E89" s="10" t="n"/>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="10" t="n"/>
+      <c r="J89" s="10" t="n"/>
+      <c r="K89" s="10" t="n"/>
+      <c r="L89" s="10" t="n"/>
+      <c r="M89" s="10" t="n"/>
+      <c r="N89" s="10" t="n"/>
+      <c r="O89" s="10" t="n"/>
+      <c r="P89" s="10" t="n"/>
+      <c r="Q89" s="10" t="n"/>
+      <c r="R89" s="10" t="n"/>
+      <c r="S89" s="10" t="n"/>
+      <c r="T89" s="10" t="n"/>
+      <c r="U89" s="10" t="n"/>
+      <c r="V89" s="10" t="n"/>
+      <c r="W89" s="10" t="n"/>
+      <c r="X89" s="10" t="n"/>
+      <c r="Y89" s="10" t="n"/>
+      <c r="Z89" s="10" t="n"/>
+      <c r="AA89" s="10" t="n"/>
+      <c r="AB89" s="10" t="n"/>
+      <c r="AC89" s="10" t="n"/>
+      <c r="AD89" s="10" t="n"/>
+      <c r="AE89" s="10" t="n"/>
+      <c r="AF89" s="10" t="n"/>
+      <c r="AG89" s="10" t="n"/>
+      <c r="AH89" s="10" t="n"/>
+      <c r="AI89" s="10" t="n"/>
+      <c r="AJ89" s="10" t="n"/>
+      <c r="AK89" s="11" t="n"/>
+    </row>
+    <row r="90" ht="108" customHeight="1">
+      <c r="C90" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_roles_permissions
 SET deleted_at = NOW(),
@@ -9455,112 +9733,46 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D87" s="10" t="n"/>
-      <c r="E87" s="10" t="n"/>
-      <c r="F87" s="10" t="n"/>
-      <c r="G87" s="10" t="n"/>
-      <c r="H87" s="10" t="n"/>
-      <c r="I87" s="10" t="n"/>
-      <c r="J87" s="10" t="n"/>
-      <c r="K87" s="10" t="n"/>
-      <c r="L87" s="10" t="n"/>
-      <c r="M87" s="10" t="n"/>
-      <c r="N87" s="10" t="n"/>
-      <c r="O87" s="10" t="n"/>
-      <c r="P87" s="10" t="n"/>
-      <c r="Q87" s="10" t="n"/>
-      <c r="R87" s="10" t="n"/>
-      <c r="S87" s="10" t="n"/>
-      <c r="T87" s="10" t="n"/>
-      <c r="U87" s="10" t="n"/>
-      <c r="V87" s="10" t="n"/>
-      <c r="W87" s="10" t="n"/>
-      <c r="X87" s="10" t="n"/>
-      <c r="Y87" s="10" t="n"/>
-      <c r="Z87" s="10" t="n"/>
-      <c r="AA87" s="10" t="n"/>
-      <c r="AB87" s="10" t="n"/>
-      <c r="AC87" s="10" t="n"/>
-      <c r="AD87" s="10" t="n"/>
-      <c r="AE87" s="10" t="n"/>
-      <c r="AF87" s="10" t="n"/>
-      <c r="AG87" s="10" t="n"/>
-      <c r="AH87" s="10" t="n"/>
-      <c r="AI87" s="10" t="n"/>
-      <c r="AJ87" s="10" t="n"/>
-      <c r="AK87" s="11" t="n"/>
-    </row>
-    <row r="88" ht="36" customHeight="1">
-      <c r="C88" s="42" t="inlineStr">
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="C91" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO m_roles_permissions (role_id, permission_id, created_at, created_by, updated_at, updated_by)
 SELECT :role_id, unnest(:permission_ids::bigint[]), NOW(), :user_account_id, NOW(), :user_account_id</t>
-        </is>
-      </c>
-      <c r="D88" s="10" t="n"/>
-      <c r="E88" s="10" t="n"/>
-      <c r="F88" s="10" t="n"/>
-      <c r="G88" s="10" t="n"/>
-      <c r="H88" s="10" t="n"/>
-      <c r="I88" s="10" t="n"/>
-      <c r="J88" s="10" t="n"/>
-      <c r="K88" s="10" t="n"/>
-      <c r="L88" s="10" t="n"/>
-      <c r="M88" s="10" t="n"/>
-      <c r="N88" s="10" t="n"/>
-      <c r="O88" s="10" t="n"/>
-      <c r="P88" s="10" t="n"/>
-      <c r="Q88" s="10" t="n"/>
-      <c r="R88" s="10" t="n"/>
-      <c r="S88" s="10" t="n"/>
-      <c r="T88" s="10" t="n"/>
-      <c r="U88" s="10" t="n"/>
-      <c r="V88" s="10" t="n"/>
-      <c r="W88" s="10" t="n"/>
-      <c r="X88" s="10" t="n"/>
-      <c r="Y88" s="10" t="n"/>
-      <c r="Z88" s="10" t="n"/>
-      <c r="AA88" s="10" t="n"/>
-      <c r="AB88" s="10" t="n"/>
-      <c r="AC88" s="10" t="n"/>
-      <c r="AD88" s="10" t="n"/>
-      <c r="AE88" s="10" t="n"/>
-      <c r="AF88" s="10" t="n"/>
-      <c r="AG88" s="10" t="n"/>
-      <c r="AH88" s="10" t="n"/>
-      <c r="AI88" s="10" t="n"/>
-      <c r="AJ88" s="10" t="n"/>
-      <c r="AK88" s="11" t="n"/>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="B89" s="27" t="inlineStr">
-        <is>
-          <t>4.5 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
-        <is>
-          <t>以下のSQLを実行して操作ログを記録する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="216" customHeight="1">
-      <c r="C91" s="42" t="inlineStr">
-        <is>
-          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
-                   gamen_name, operation, result_status,
-                   target_id, target_table,
-                   before_value, after_value,
-                   error_message, stack_trace,
-                   ip_address, user_agent)
-VALUES (1, NOW(), :account_id, :ja_id,
-        'ロール管理画面 (ACSMS-SCR-027)', 'UPDATE', 1,
-        :role_id, 'm_roles',
-        :before_value_json, :after_value_json,
-        '', '',
-        :ip_address, :user_agent)</t>
         </is>
       </c>
       <c r="D91" s="10" t="n"/>
@@ -9598,8 +9810,74 @@
       <c r="AJ91" s="10" t="n"/>
       <c r="AK91" s="11" t="n"/>
     </row>
-    <row r="92" ht="162" customHeight="1">
-      <c r="C92" s="42" t="inlineStr">
+    <row r="92" ht="18" customHeight="1">
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>4.5 操作ログ記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="C93" s="41" t="inlineStr">
+        <is>
+          <t>以下のSQLを実行して操作ログを記録する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="216" customHeight="1">
+      <c r="C94" s="42" t="inlineStr">
+        <is>
+          <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
+                   gamen_name, operation, result_status,
+                   target_id, target_table,
+                   before_value, after_value,
+                   error_message, stack_trace,
+                   ip_address, user_agent)
+VALUES (1, NOW(), :account_id, :ja_id,
+        'ロール管理画面 (ACSMS-SCR-027)', 'UPDATE', 1,
+        :role_id, 'm_roles',
+        :before_value_json, :after_value_json,
+        '', '',
+        :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="n"/>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="10" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="10" t="n"/>
+      <c r="Y94" s="10" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="11" t="n"/>
+    </row>
+    <row r="95" ht="162" customHeight="1">
+      <c r="C95" s="42" t="inlineStr">
         <is>
           <t>`before_value`：更新前のデータをJSON形式で格納する。
 {
@@ -9611,43 +9889,43 @@
 }</t>
         </is>
       </c>
-      <c r="D92" s="10" t="n"/>
-      <c r="E92" s="10" t="n"/>
-      <c r="F92" s="10" t="n"/>
-      <c r="G92" s="10" t="n"/>
-      <c r="H92" s="10" t="n"/>
-      <c r="I92" s="10" t="n"/>
-      <c r="J92" s="10" t="n"/>
-      <c r="K92" s="10" t="n"/>
-      <c r="L92" s="10" t="n"/>
-      <c r="M92" s="10" t="n"/>
-      <c r="N92" s="10" t="n"/>
-      <c r="O92" s="10" t="n"/>
-      <c r="P92" s="10" t="n"/>
-      <c r="Q92" s="10" t="n"/>
-      <c r="R92" s="10" t="n"/>
-      <c r="S92" s="10" t="n"/>
-      <c r="T92" s="10" t="n"/>
-      <c r="U92" s="10" t="n"/>
-      <c r="V92" s="10" t="n"/>
-      <c r="W92" s="10" t="n"/>
-      <c r="X92" s="10" t="n"/>
-      <c r="Y92" s="10" t="n"/>
-      <c r="Z92" s="10" t="n"/>
-      <c r="AA92" s="10" t="n"/>
-      <c r="AB92" s="10" t="n"/>
-      <c r="AC92" s="10" t="n"/>
-      <c r="AD92" s="10" t="n"/>
-      <c r="AE92" s="10" t="n"/>
-      <c r="AF92" s="10" t="n"/>
-      <c r="AG92" s="10" t="n"/>
-      <c r="AH92" s="10" t="n"/>
-      <c r="AI92" s="10" t="n"/>
-      <c r="AJ92" s="10" t="n"/>
-      <c r="AK92" s="11" t="n"/>
-    </row>
-    <row r="93" ht="162" customHeight="1">
-      <c r="C93" s="42" t="inlineStr">
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="10" t="n"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="10" t="n"/>
+      <c r="I95" s="10" t="n"/>
+      <c r="J95" s="10" t="n"/>
+      <c r="K95" s="10" t="n"/>
+      <c r="L95" s="10" t="n"/>
+      <c r="M95" s="10" t="n"/>
+      <c r="N95" s="10" t="n"/>
+      <c r="O95" s="10" t="n"/>
+      <c r="P95" s="10" t="n"/>
+      <c r="Q95" s="10" t="n"/>
+      <c r="R95" s="10" t="n"/>
+      <c r="S95" s="10" t="n"/>
+      <c r="T95" s="10" t="n"/>
+      <c r="U95" s="10" t="n"/>
+      <c r="V95" s="10" t="n"/>
+      <c r="W95" s="10" t="n"/>
+      <c r="X95" s="10" t="n"/>
+      <c r="Y95" s="10" t="n"/>
+      <c r="Z95" s="10" t="n"/>
+      <c r="AA95" s="10" t="n"/>
+      <c r="AB95" s="10" t="n"/>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="10" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="10" t="n"/>
+      <c r="AK95" s="11" t="n"/>
+    </row>
+    <row r="96" ht="162" customHeight="1">
+      <c r="C96" s="42" t="inlineStr">
         <is>
           <t>`after_value`：更新後のデータをJSON形式で格納する。
 {
@@ -9659,78 +9937,78 @@
 }</t>
         </is>
       </c>
-      <c r="D93" s="10" t="n"/>
-      <c r="E93" s="10" t="n"/>
-      <c r="F93" s="10" t="n"/>
-      <c r="G93" s="10" t="n"/>
-      <c r="H93" s="10" t="n"/>
-      <c r="I93" s="10" t="n"/>
-      <c r="J93" s="10" t="n"/>
-      <c r="K93" s="10" t="n"/>
-      <c r="L93" s="10" t="n"/>
-      <c r="M93" s="10" t="n"/>
-      <c r="N93" s="10" t="n"/>
-      <c r="O93" s="10" t="n"/>
-      <c r="P93" s="10" t="n"/>
-      <c r="Q93" s="10" t="n"/>
-      <c r="R93" s="10" t="n"/>
-      <c r="S93" s="10" t="n"/>
-      <c r="T93" s="10" t="n"/>
-      <c r="U93" s="10" t="n"/>
-      <c r="V93" s="10" t="n"/>
-      <c r="W93" s="10" t="n"/>
-      <c r="X93" s="10" t="n"/>
-      <c r="Y93" s="10" t="n"/>
-      <c r="Z93" s="10" t="n"/>
-      <c r="AA93" s="10" t="n"/>
-      <c r="AB93" s="10" t="n"/>
-      <c r="AC93" s="10" t="n"/>
-      <c r="AD93" s="10" t="n"/>
-      <c r="AE93" s="10" t="n"/>
-      <c r="AF93" s="10" t="n"/>
-      <c r="AG93" s="10" t="n"/>
-      <c r="AH93" s="10" t="n"/>
-      <c r="AI93" s="10" t="n"/>
-      <c r="AJ93" s="10" t="n"/>
-      <c r="AK93" s="11" t="n"/>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="B94" s="27" t="inlineStr">
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="10" t="n"/>
+      <c r="I96" s="10" t="n"/>
+      <c r="J96" s="10" t="n"/>
+      <c r="K96" s="10" t="n"/>
+      <c r="L96" s="10" t="n"/>
+      <c r="M96" s="10" t="n"/>
+      <c r="N96" s="10" t="n"/>
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="10" t="n"/>
+      <c r="Q96" s="10" t="n"/>
+      <c r="R96" s="10" t="n"/>
+      <c r="S96" s="10" t="n"/>
+      <c r="T96" s="10" t="n"/>
+      <c r="U96" s="10" t="n"/>
+      <c r="V96" s="10" t="n"/>
+      <c r="W96" s="10" t="n"/>
+      <c r="X96" s="10" t="n"/>
+      <c r="Y96" s="10" t="n"/>
+      <c r="Z96" s="10" t="n"/>
+      <c r="AA96" s="10" t="n"/>
+      <c r="AB96" s="10" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="10" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="10" t="n"/>
+      <c r="AK96" s="11" t="n"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="B97" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>更新されたデータをdata オブジェクトとして返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="B96" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="C97" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="C98" s="41" t="inlineStr">
         <is>
+          <t>更新されたデータをdata オブジェクトとして返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="B99" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="C100" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="C101" s="41" t="inlineStr">
+        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="216" customHeight="1">
-      <c r="C99" s="42" t="inlineStr">
+    <row r="102" ht="216" customHeight="1">
+      <c r="C102" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9746,77 +10024,77 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D99" s="10" t="n"/>
-      <c r="E99" s="10" t="n"/>
-      <c r="F99" s="10" t="n"/>
-      <c r="G99" s="10" t="n"/>
-      <c r="H99" s="10" t="n"/>
-      <c r="I99" s="10" t="n"/>
-      <c r="J99" s="10" t="n"/>
-      <c r="K99" s="10" t="n"/>
-      <c r="L99" s="10" t="n"/>
-      <c r="M99" s="10" t="n"/>
-      <c r="N99" s="10" t="n"/>
-      <c r="O99" s="10" t="n"/>
-      <c r="P99" s="10" t="n"/>
-      <c r="Q99" s="10" t="n"/>
-      <c r="R99" s="10" t="n"/>
-      <c r="S99" s="10" t="n"/>
-      <c r="T99" s="10" t="n"/>
-      <c r="U99" s="10" t="n"/>
-      <c r="V99" s="10" t="n"/>
-      <c r="W99" s="10" t="n"/>
-      <c r="X99" s="10" t="n"/>
-      <c r="Y99" s="10" t="n"/>
-      <c r="Z99" s="10" t="n"/>
-      <c r="AA99" s="10" t="n"/>
-      <c r="AB99" s="10" t="n"/>
-      <c r="AC99" s="10" t="n"/>
-      <c r="AD99" s="10" t="n"/>
-      <c r="AE99" s="10" t="n"/>
-      <c r="AF99" s="10" t="n"/>
-      <c r="AG99" s="10" t="n"/>
-      <c r="AH99" s="10" t="n"/>
-      <c r="AI99" s="10" t="n"/>
-      <c r="AJ99" s="10" t="n"/>
-      <c r="AK99" s="11" t="n"/>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="10" t="n"/>
+      <c r="J102" s="10" t="n"/>
+      <c r="K102" s="10" t="n"/>
+      <c r="L102" s="10" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="10" t="n"/>
+      <c r="W102" s="10" t="n"/>
+      <c r="X102" s="10" t="n"/>
+      <c r="Y102" s="10" t="n"/>
+      <c r="Z102" s="10" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="10" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="10" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="10" t="n"/>
+      <c r="AK102" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="185">
+  <mergeCells count="192">
     <mergeCell ref="J11:AK11"/>
-    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T24:X24"/>
-    <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="B54:I54"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
-    <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="C86:AK86"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="D73:AK73"/>
-    <mergeCell ref="A63:AK63"/>
-    <mergeCell ref="C45:AK45"/>
+    <mergeCell ref="D82:AK82"/>
     <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="C85:AK85"/>
+    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="D33:L33"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
@@ -9824,33 +10102,39 @@
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="D35:L35"/>
+    <mergeCell ref="C46:AK46"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="C51:AK51"/>
     <mergeCell ref="C95:AK95"/>
     <mergeCell ref="D34:L34"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="M25:P25"/>
-    <mergeCell ref="C48:AK48"/>
+    <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="B45:I45"/>
     <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D75:AK75"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="A21:AK21"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="D72:AK72"/>
+    <mergeCell ref="B77:AK77"/>
     <mergeCell ref="T38:X38"/>
+    <mergeCell ref="C33:C40"/>
+    <mergeCell ref="C49:AK49"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="C42:AK42"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="C88:AK88"/>
+    <mergeCell ref="B69:AK69"/>
     <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
@@ -9858,32 +10142,33 @@
     <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="D79:AK79"/>
+    <mergeCell ref="A67:AK67"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="C99:AK99"/>
+    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="D38:L38"/>
+    <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
+    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
-    <mergeCell ref="B64:AK64"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="B89:AK89"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
+    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="C52:AK52"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="Y31:AE31"/>
-    <mergeCell ref="B81:AK81"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="B63:I63"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
@@ -9891,37 +10176,41 @@
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="C78:AK78"/>
     <mergeCell ref="T32:X32"/>
-    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="C98:AK98"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="A29:AK29"/>
     <mergeCell ref="B11:I11"/>
+    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="M34:P34"/>
+    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="C54:AK54"/>
+    <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="B84:AK84"/>
     <mergeCell ref="C93:AK93"/>
     <mergeCell ref="T26:X26"/>
+    <mergeCell ref="B92:AK92"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="C33:C39"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
+    <mergeCell ref="C43:AK43"/>
     <mergeCell ref="J9:AK9"/>
-    <mergeCell ref="B94:AK94"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
@@ -9932,41 +10221,37 @@
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
-    <mergeCell ref="B96:AK96"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="B14:I19"/>
     <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q40:S40"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="C83:AK83"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="T35:X35"/>
-    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="D74:AK74"/>
     <mergeCell ref="Y32:AE32"/>
-    <mergeCell ref="D68:AK68"/>
     <mergeCell ref="T25:X25"/>
-    <mergeCell ref="C97:AK97"/>
-    <mergeCell ref="D67:AK67"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B60:I60"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B99:AK99"/>
     <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="D69:AK69"/>
+    <mergeCell ref="B68:AK68"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="C76:AK76"/>
-    <mergeCell ref="B75:AK75"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="D70:AK70"/>
+    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M37:P37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9979,7 +10264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AK63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -10140,7 +10425,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11450,7 +11735,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -11464,33 +11749,40 @@
     <row r="54" ht="36" customHeight="1">
       <c r="C54" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：ログインユーザーの role_code が `NICHINO_ADMIN` であるか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
+          <t>権限チェック：`@Permissions('role.view')`（`seeder.md §2.14` permission_id=45）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
       <c r="D55" s="41" t="inlineStr">
         <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="C56" s="41" t="inlineStr">
+          <t>`m_roles_permissions` 上 `role.view` は NICHINO_ADMIN にのみ付与されているため、</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="D56" s="41" t="inlineStr">
+        <is>
+          <t>実装は他コントローラと同じく `PermissionsGuard` + `@Permissions(...)` を使用し、</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="C57" s="41" t="inlineStr">
         <is>
           <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="B57" s="27" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="72" customHeight="1">
-      <c r="C58" s="42" t="inlineStr">
+    <row r="59" ht="72" customHeight="1">
+      <c r="C59" s="42" t="inlineStr">
         <is>
           <t>SELECT permission_id, permission_code, permission_name, description
 FROM m_permissions
@@ -11498,79 +11790,79 @@
 ORDER BY permission_id ASC</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="10" t="n"/>
-      <c r="M58" s="10" t="n"/>
-      <c r="N58" s="10" t="n"/>
-      <c r="O58" s="10" t="n"/>
-      <c r="P58" s="10" t="n"/>
-      <c r="Q58" s="10" t="n"/>
-      <c r="R58" s="10" t="n"/>
-      <c r="S58" s="10" t="n"/>
-      <c r="T58" s="10" t="n"/>
-      <c r="U58" s="10" t="n"/>
-      <c r="V58" s="10" t="n"/>
-      <c r="W58" s="10" t="n"/>
-      <c r="X58" s="10" t="n"/>
-      <c r="Y58" s="10" t="n"/>
-      <c r="Z58" s="10" t="n"/>
-      <c r="AA58" s="10" t="n"/>
-      <c r="AB58" s="10" t="n"/>
-      <c r="AC58" s="10" t="n"/>
-      <c r="AD58" s="10" t="n"/>
-      <c r="AE58" s="10" t="n"/>
-      <c r="AF58" s="10" t="n"/>
-      <c r="AG58" s="10" t="n"/>
-      <c r="AH58" s="10" t="n"/>
-      <c r="AI58" s="10" t="n"/>
-      <c r="AJ58" s="10" t="n"/>
-      <c r="AK58" s="11" t="n"/>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="B59" s="27" t="inlineStr">
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="n"/>
+      <c r="J59" s="10" t="n"/>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="10" t="n"/>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="10" t="n"/>
+      <c r="X59" s="10" t="n"/>
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="10" t="n"/>
+      <c r="AE59" s="10" t="n"/>
+      <c r="AF59" s="10" t="n"/>
+      <c r="AG59" s="10" t="n"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="10" t="n"/>
+      <c r="AJ59" s="10" t="n"/>
+      <c r="AK59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>4.4 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="C60" s="41" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="C61" s="41" t="inlineStr">
         <is>
           <t>取得結果を data 配列として返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="B61" s="27" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="C62" s="41" t="inlineStr">
+    <row r="63" ht="18" customHeight="1">
+      <c r="C63" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="109">
+  <mergeCells count="110">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y27:AE27"/>
+    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C53:AK53"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="AF21:AK21"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="C45:AK45"/>
@@ -11593,9 +11885,9 @@
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="A23:AK23"/>
     <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="D56:AK56"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="C33:AK33"/>
-    <mergeCell ref="B61:AK61"/>
     <mergeCell ref="C42:AK42"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
@@ -11609,22 +11901,24 @@
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="C52:AK52"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M21:P21"/>
+    <mergeCell ref="C61:AK61"/>
     <mergeCell ref="C39:AK39"/>
     <mergeCell ref="B41:I41"/>
     <mergeCell ref="B35:I35"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="D27:L27"/>
+    <mergeCell ref="B58:AK58"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="C62:AK62"/>
-    <mergeCell ref="B57:AK57"/>
+    <mergeCell ref="B60:AK60"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
@@ -11633,13 +11927,13 @@
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C54:AK54"/>
     <mergeCell ref="D30:L30"/>
+    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="T21:X21"/>
     <mergeCell ref="C50:AK50"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AH1:AK1"/>
@@ -11665,12 +11959,11 @@
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="C21:L21"/>
+    <mergeCell ref="B62:AK62"/>
     <mergeCell ref="M28:P28"/>
-    <mergeCell ref="B59:AK59"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
